--- a/liga_classica/datasets_liga_classica/links_times_cartola_liga_classica.xlsx
+++ b/liga_classica/datasets_liga_classica/links_times_cartola_liga_classica.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t>Nome do Time</t>
   </si>
@@ -136,6 +136,9 @@
     <t>Rolo Compressor ZN</t>
   </si>
   <si>
+    <t>RS Expressões da Arte</t>
+  </si>
+  <si>
     <t>S.E.R. GRILLO</t>
   </si>
   <si>
@@ -290,6 +293,9 @@
   </si>
   <si>
     <t>https://cartola.globo.com/#!/time/18223508</t>
+  </si>
+  <si>
+    <t>https://cartola.globo.com/#!/time/896842</t>
   </si>
   <si>
     <t>https://cartola.globo.com/#!/time/5823700</t>
@@ -705,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -727,7 +733,7 @@
         <v>117598</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -738,7 +744,7 @@
         <v>49355335</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -749,7 +755,7 @@
         <v>18346776</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -760,7 +766,7 @@
         <v>13913874</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -771,7 +777,7 @@
         <v>50988641</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -782,7 +788,7 @@
         <v>25748736</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -793,7 +799,7 @@
         <v>3851966</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -804,7 +810,7 @@
         <v>49243759</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -815,7 +821,7 @@
         <v>7017989</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -826,7 +832,7 @@
         <v>387186</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -837,7 +843,7 @@
         <v>20696550</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -848,7 +854,7 @@
         <v>186283</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -859,7 +865,7 @@
         <v>1863710</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -870,7 +876,7 @@
         <v>48279389</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -881,7 +887,7 @@
         <v>25311459</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -892,7 +898,7 @@
         <v>18642587</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -903,7 +909,7 @@
         <v>25565675</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -914,7 +920,7 @@
         <v>18344271</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -925,7 +931,7 @@
         <v>18421230</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -936,7 +942,7 @@
         <v>528730</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -947,7 +953,7 @@
         <v>24468241</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -958,7 +964,7 @@
         <v>13951133</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -969,7 +975,7 @@
         <v>1747619</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -980,7 +986,7 @@
         <v>51010813</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -991,7 +997,7 @@
         <v>44810918</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1002,7 +1008,7 @@
         <v>20340994</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1013,7 +1019,7 @@
         <v>4911779</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1024,7 +1030,7 @@
         <v>19033717</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1035,7 +1041,7 @@
         <v>25401606</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1046,7 +1052,7 @@
         <v>30267301</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1057,7 +1063,7 @@
         <v>3708025</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1068,7 +1074,7 @@
         <v>14124559</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1079,7 +1085,7 @@
         <v>48498051</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1090,7 +1096,7 @@
         <v>25313333</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1101,7 +1107,7 @@
         <v>9823692</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1112,7 +1118,7 @@
         <v>3447341</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1123,7 +1129,7 @@
         <v>18223508</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1131,10 +1137,10 @@
         <v>40</v>
       </c>
       <c r="B39">
-        <v>5823700</v>
+        <v>896842</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1142,10 +1148,10 @@
         <v>41</v>
       </c>
       <c r="B40">
-        <v>29228373</v>
+        <v>5823700</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1153,10 +1159,10 @@
         <v>42</v>
       </c>
       <c r="B41">
-        <v>25811332</v>
+        <v>29228373</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1164,10 +1170,10 @@
         <v>43</v>
       </c>
       <c r="B42">
-        <v>1148959</v>
+        <v>25811332</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1175,10 +1181,10 @@
         <v>44</v>
       </c>
       <c r="B43">
-        <v>13707047</v>
+        <v>1148959</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1186,10 +1192,10 @@
         <v>45</v>
       </c>
       <c r="B44">
-        <v>4229593</v>
+        <v>13707047</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1197,10 +1203,10 @@
         <v>46</v>
       </c>
       <c r="B45">
-        <v>28741323</v>
+        <v>4229593</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1208,10 +1214,10 @@
         <v>47</v>
       </c>
       <c r="B46">
-        <v>49180400</v>
+        <v>28741323</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1219,10 +1225,10 @@
         <v>48</v>
       </c>
       <c r="B47">
-        <v>212042</v>
+        <v>49180400</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1230,10 +1236,10 @@
         <v>49</v>
       </c>
       <c r="B48">
-        <v>479510</v>
+        <v>212042</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1241,10 +1247,10 @@
         <v>50</v>
       </c>
       <c r="B49">
-        <v>335716</v>
+        <v>479510</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1252,10 +1258,10 @@
         <v>51</v>
       </c>
       <c r="B50">
-        <v>1273719</v>
+        <v>335716</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1263,10 +1269,10 @@
         <v>52</v>
       </c>
       <c r="B51">
-        <v>3424598</v>
+        <v>1273719</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1274,10 +1280,10 @@
         <v>53</v>
       </c>
       <c r="B52">
-        <v>2981301</v>
+        <v>3424598</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1285,10 +1291,21 @@
         <v>54</v>
       </c>
       <c r="B53">
+        <v>2981301</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54">
         <v>14696986</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>106</v>
+      <c r="C54" s="2" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1330,21 +1347,22 @@
     <hyperlink ref="C36" r:id="rId35" location="!/time/9823692"/>
     <hyperlink ref="C37" r:id="rId36" location="!/time/3447341"/>
     <hyperlink ref="C38" r:id="rId37" location="!/time/18223508"/>
-    <hyperlink ref="C39" r:id="rId38" location="!/time/5823700"/>
-    <hyperlink ref="C40" r:id="rId39" location="!/time/29228373"/>
-    <hyperlink ref="C41" r:id="rId40" location="!/time/25811332"/>
-    <hyperlink ref="C42" r:id="rId41" location="!/time/1148959"/>
-    <hyperlink ref="C43" r:id="rId42" location="!/time/13707047"/>
-    <hyperlink ref="C44" r:id="rId43" location="!/time/4229593"/>
-    <hyperlink ref="C45" r:id="rId44" location="!/time/28741323"/>
-    <hyperlink ref="C46" r:id="rId45" location="!/time/49180400"/>
-    <hyperlink ref="C47" r:id="rId46" location="!/time/212042"/>
-    <hyperlink ref="C48" r:id="rId47" location="!/time/479510"/>
-    <hyperlink ref="C49" r:id="rId48" location="!/time/335716"/>
-    <hyperlink ref="C50" r:id="rId49" location="!/time/1273719"/>
-    <hyperlink ref="C51" r:id="rId50" location="!/time/3424598"/>
-    <hyperlink ref="C52" r:id="rId51" location="!/time/2981301"/>
-    <hyperlink ref="C53" r:id="rId52" location="!/time/14696986"/>
+    <hyperlink ref="C39" r:id="rId38" location="!/time/896842"/>
+    <hyperlink ref="C40" r:id="rId39" location="!/time/5823700"/>
+    <hyperlink ref="C41" r:id="rId40" location="!/time/29228373"/>
+    <hyperlink ref="C42" r:id="rId41" location="!/time/25811332"/>
+    <hyperlink ref="C43" r:id="rId42" location="!/time/1148959"/>
+    <hyperlink ref="C44" r:id="rId43" location="!/time/13707047"/>
+    <hyperlink ref="C45" r:id="rId44" location="!/time/4229593"/>
+    <hyperlink ref="C46" r:id="rId45" location="!/time/28741323"/>
+    <hyperlink ref="C47" r:id="rId46" location="!/time/49180400"/>
+    <hyperlink ref="C48" r:id="rId47" location="!/time/212042"/>
+    <hyperlink ref="C49" r:id="rId48" location="!/time/479510"/>
+    <hyperlink ref="C50" r:id="rId49" location="!/time/335716"/>
+    <hyperlink ref="C51" r:id="rId50" location="!/time/1273719"/>
+    <hyperlink ref="C52" r:id="rId51" location="!/time/3424598"/>
+    <hyperlink ref="C53" r:id="rId52" location="!/time/2981301"/>
+    <hyperlink ref="C54" r:id="rId53" location="!/time/14696986"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/liga_classica/datasets_liga_classica/links_times_cartola_liga_classica.xlsx
+++ b/liga_classica/datasets_liga_classica/links_times_cartola_liga_classica.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
   <si>
     <t>Nome do Time</t>
   </si>
@@ -115,9 +115,6 @@
     <t>Máquina Laranjja</t>
   </si>
   <si>
-    <t>NaoVaiDescer!</t>
-  </si>
-  <si>
     <t>Paulo Virgili FC</t>
   </si>
   <si>
@@ -272,9 +269,6 @@
   </si>
   <si>
     <t>https://cartola.globo.com/#!/time/30267301</t>
-  </si>
-  <si>
-    <t>https://cartola.globo.com/#!/time/3708025</t>
   </si>
   <si>
     <t>https://cartola.globo.com/#!/time/14124559</t>
@@ -711,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -733,7 +727,7 @@
         <v>117598</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -744,7 +738,7 @@
         <v>49355335</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -755,7 +749,7 @@
         <v>18346776</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -766,7 +760,7 @@
         <v>13913874</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -777,7 +771,7 @@
         <v>50988641</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -788,7 +782,7 @@
         <v>25748736</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -799,7 +793,7 @@
         <v>3851966</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -810,7 +804,7 @@
         <v>49243759</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -821,7 +815,7 @@
         <v>7017989</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -832,7 +826,7 @@
         <v>387186</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -843,7 +837,7 @@
         <v>20696550</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -854,7 +848,7 @@
         <v>186283</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -865,7 +859,7 @@
         <v>1863710</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -876,7 +870,7 @@
         <v>48279389</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -887,7 +881,7 @@
         <v>25311459</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -898,7 +892,7 @@
         <v>18642587</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -909,7 +903,7 @@
         <v>25565675</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -920,7 +914,7 @@
         <v>18344271</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -931,7 +925,7 @@
         <v>18421230</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -942,7 +936,7 @@
         <v>528730</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -953,7 +947,7 @@
         <v>24468241</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -964,7 +958,7 @@
         <v>13951133</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -975,7 +969,7 @@
         <v>1747619</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -986,7 +980,7 @@
         <v>51010813</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -997,7 +991,7 @@
         <v>44810918</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1008,7 +1002,7 @@
         <v>20340994</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1019,7 +1013,7 @@
         <v>4911779</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1030,7 +1024,7 @@
         <v>19033717</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1041,7 +1035,7 @@
         <v>25401606</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1052,7 +1046,7 @@
         <v>30267301</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1060,10 +1054,10 @@
         <v>33</v>
       </c>
       <c r="B32">
-        <v>3708025</v>
+        <v>14124559</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1071,10 +1065,10 @@
         <v>34</v>
       </c>
       <c r="B33">
-        <v>14124559</v>
+        <v>48498051</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1082,10 +1076,10 @@
         <v>35</v>
       </c>
       <c r="B34">
-        <v>48498051</v>
+        <v>25313333</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1093,10 +1087,10 @@
         <v>36</v>
       </c>
       <c r="B35">
-        <v>25313333</v>
+        <v>9823692</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1104,10 +1098,10 @@
         <v>37</v>
       </c>
       <c r="B36">
-        <v>9823692</v>
+        <v>3447341</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1115,10 +1109,10 @@
         <v>38</v>
       </c>
       <c r="B37">
-        <v>3447341</v>
+        <v>18223508</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1126,10 +1120,10 @@
         <v>39</v>
       </c>
       <c r="B38">
-        <v>18223508</v>
+        <v>896842</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1137,10 +1131,10 @@
         <v>40</v>
       </c>
       <c r="B39">
-        <v>896842</v>
+        <v>5823700</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1148,10 +1142,10 @@
         <v>41</v>
       </c>
       <c r="B40">
-        <v>5823700</v>
+        <v>29228373</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1159,10 +1153,10 @@
         <v>42</v>
       </c>
       <c r="B41">
-        <v>29228373</v>
+        <v>25811332</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1170,10 +1164,10 @@
         <v>43</v>
       </c>
       <c r="B42">
-        <v>25811332</v>
+        <v>1148959</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1181,10 +1175,10 @@
         <v>44</v>
       </c>
       <c r="B43">
-        <v>1148959</v>
+        <v>13707047</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1192,10 +1186,10 @@
         <v>45</v>
       </c>
       <c r="B44">
-        <v>13707047</v>
+        <v>4229593</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1203,10 +1197,10 @@
         <v>46</v>
       </c>
       <c r="B45">
-        <v>4229593</v>
+        <v>28741323</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1214,10 +1208,10 @@
         <v>47</v>
       </c>
       <c r="B46">
-        <v>28741323</v>
+        <v>49180400</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1225,10 +1219,10 @@
         <v>48</v>
       </c>
       <c r="B47">
-        <v>49180400</v>
+        <v>212042</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1236,10 +1230,10 @@
         <v>49</v>
       </c>
       <c r="B48">
-        <v>212042</v>
+        <v>479510</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1247,10 +1241,10 @@
         <v>50</v>
       </c>
       <c r="B49">
-        <v>479510</v>
+        <v>335716</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1258,10 +1252,10 @@
         <v>51</v>
       </c>
       <c r="B50">
-        <v>335716</v>
+        <v>1273719</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1269,10 +1263,10 @@
         <v>52</v>
       </c>
       <c r="B51">
-        <v>1273719</v>
+        <v>3424598</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1280,10 +1274,10 @@
         <v>53</v>
       </c>
       <c r="B52">
-        <v>3424598</v>
+        <v>2981301</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1291,21 +1285,10 @@
         <v>54</v>
       </c>
       <c r="B53">
-        <v>2981301</v>
+        <v>14696986</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" t="s">
-        <v>55</v>
-      </c>
-      <c r="B54">
-        <v>14696986</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1340,29 +1323,28 @@
     <hyperlink ref="C29" r:id="rId28" location="!/time/19033717"/>
     <hyperlink ref="C30" r:id="rId29" location="!/time/25401606"/>
     <hyperlink ref="C31" r:id="rId30" location="!/time/30267301"/>
-    <hyperlink ref="C32" r:id="rId31" location="!/time/3708025"/>
-    <hyperlink ref="C33" r:id="rId32" location="!/time/14124559"/>
-    <hyperlink ref="C34" r:id="rId33" location="!/time/48498051"/>
-    <hyperlink ref="C35" r:id="rId34" location="!/time/25313333"/>
-    <hyperlink ref="C36" r:id="rId35" location="!/time/9823692"/>
-    <hyperlink ref="C37" r:id="rId36" location="!/time/3447341"/>
-    <hyperlink ref="C38" r:id="rId37" location="!/time/18223508"/>
-    <hyperlink ref="C39" r:id="rId38" location="!/time/896842"/>
-    <hyperlink ref="C40" r:id="rId39" location="!/time/5823700"/>
-    <hyperlink ref="C41" r:id="rId40" location="!/time/29228373"/>
-    <hyperlink ref="C42" r:id="rId41" location="!/time/25811332"/>
-    <hyperlink ref="C43" r:id="rId42" location="!/time/1148959"/>
-    <hyperlink ref="C44" r:id="rId43" location="!/time/13707047"/>
-    <hyperlink ref="C45" r:id="rId44" location="!/time/4229593"/>
-    <hyperlink ref="C46" r:id="rId45" location="!/time/28741323"/>
-    <hyperlink ref="C47" r:id="rId46" location="!/time/49180400"/>
-    <hyperlink ref="C48" r:id="rId47" location="!/time/212042"/>
-    <hyperlink ref="C49" r:id="rId48" location="!/time/479510"/>
-    <hyperlink ref="C50" r:id="rId49" location="!/time/335716"/>
-    <hyperlink ref="C51" r:id="rId50" location="!/time/1273719"/>
-    <hyperlink ref="C52" r:id="rId51" location="!/time/3424598"/>
-    <hyperlink ref="C53" r:id="rId52" location="!/time/2981301"/>
-    <hyperlink ref="C54" r:id="rId53" location="!/time/14696986"/>
+    <hyperlink ref="C32" r:id="rId31" location="!/time/14124559"/>
+    <hyperlink ref="C33" r:id="rId32" location="!/time/48498051"/>
+    <hyperlink ref="C34" r:id="rId33" location="!/time/25313333"/>
+    <hyperlink ref="C35" r:id="rId34" location="!/time/9823692"/>
+    <hyperlink ref="C36" r:id="rId35" location="!/time/3447341"/>
+    <hyperlink ref="C37" r:id="rId36" location="!/time/18223508"/>
+    <hyperlink ref="C38" r:id="rId37" location="!/time/896842"/>
+    <hyperlink ref="C39" r:id="rId38" location="!/time/5823700"/>
+    <hyperlink ref="C40" r:id="rId39" location="!/time/29228373"/>
+    <hyperlink ref="C41" r:id="rId40" location="!/time/25811332"/>
+    <hyperlink ref="C42" r:id="rId41" location="!/time/1148959"/>
+    <hyperlink ref="C43" r:id="rId42" location="!/time/13707047"/>
+    <hyperlink ref="C44" r:id="rId43" location="!/time/4229593"/>
+    <hyperlink ref="C45" r:id="rId44" location="!/time/28741323"/>
+    <hyperlink ref="C46" r:id="rId45" location="!/time/49180400"/>
+    <hyperlink ref="C47" r:id="rId46" location="!/time/212042"/>
+    <hyperlink ref="C48" r:id="rId47" location="!/time/479510"/>
+    <hyperlink ref="C49" r:id="rId48" location="!/time/335716"/>
+    <hyperlink ref="C50" r:id="rId49" location="!/time/1273719"/>
+    <hyperlink ref="C51" r:id="rId50" location="!/time/3424598"/>
+    <hyperlink ref="C52" r:id="rId51" location="!/time/2981301"/>
+    <hyperlink ref="C53" r:id="rId52" location="!/time/14696986"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/liga_classica/datasets_liga_classica/links_times_cartola_liga_classica.xlsx
+++ b/liga_classica/datasets_liga_classica/links_times_cartola_liga_classica.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t>Nome do Time</t>
   </si>
@@ -64,9 +64,6 @@
     <t>FBC Colorado II</t>
   </si>
   <si>
-    <t>FC castelo Branco 2</t>
-  </si>
-  <si>
     <t>FC Los Castilho</t>
   </si>
   <si>
@@ -88,6 +85,9 @@
     <t>Grêmio imortal 37</t>
   </si>
   <si>
+    <t>HVCARTOLA</t>
+  </si>
+  <si>
     <t>JUV. KP</t>
   </si>
   <si>
@@ -178,6 +178,9 @@
     <t>Time do S.A.P.O</t>
   </si>
   <si>
+    <t>VaiDescerkkkk!!!</t>
+  </si>
+  <si>
     <t>VASCO MARTINS FC</t>
   </si>
   <si>
@@ -220,9 +223,6 @@
     <t>https://cartola.globo.com/#!/time/1863710</t>
   </si>
   <si>
-    <t>https://cartola.globo.com/#!/time/48279389</t>
-  </si>
-  <si>
     <t>https://cartola.globo.com/#!/time/25311459</t>
   </si>
   <si>
@@ -244,6 +244,9 @@
     <t>https://cartola.globo.com/#!/time/24468241</t>
   </si>
   <si>
+    <t>https://cartola.globo.com/#!/time/26243123</t>
+  </si>
+  <si>
     <t>https://cartola.globo.com/#!/time/13951133</t>
   </si>
   <si>
@@ -332,6 +335,9 @@
   </si>
   <si>
     <t>https://cartola.globo.com/#!/time/2981301</t>
+  </si>
+  <si>
+    <t>https://cartola.globo.com/#!/time/3708025</t>
   </si>
   <si>
     <t>https://cartola.globo.com/#!/time/14696986</t>
@@ -705,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -727,7 +733,7 @@
         <v>117598</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -738,7 +744,7 @@
         <v>49355335</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -749,7 +755,7 @@
         <v>18346776</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -760,7 +766,7 @@
         <v>13913874</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -771,7 +777,7 @@
         <v>50988641</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -782,7 +788,7 @@
         <v>25748736</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -793,7 +799,7 @@
         <v>3851966</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -804,7 +810,7 @@
         <v>49243759</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -815,7 +821,7 @@
         <v>7017989</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -826,7 +832,7 @@
         <v>387186</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -837,7 +843,7 @@
         <v>20696550</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -848,7 +854,7 @@
         <v>186283</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -859,7 +865,7 @@
         <v>1863710</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -867,10 +873,10 @@
         <v>16</v>
       </c>
       <c r="B15">
-        <v>48279389</v>
+        <v>25311459</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -878,10 +884,10 @@
         <v>17</v>
       </c>
       <c r="B16">
-        <v>25311459</v>
+        <v>18642587</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -889,10 +895,10 @@
         <v>18</v>
       </c>
       <c r="B17">
-        <v>18642587</v>
+        <v>25565675</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -900,10 +906,10 @@
         <v>19</v>
       </c>
       <c r="B18">
-        <v>25565675</v>
+        <v>18344271</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -911,10 +917,10 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>18344271</v>
+        <v>18421230</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -922,10 +928,10 @@
         <v>21</v>
       </c>
       <c r="B20">
-        <v>18421230</v>
+        <v>528730</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -933,10 +939,10 @@
         <v>22</v>
       </c>
       <c r="B21">
-        <v>528730</v>
+        <v>24468241</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -944,10 +950,10 @@
         <v>23</v>
       </c>
       <c r="B22">
-        <v>24468241</v>
+        <v>26243123</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -958,7 +964,7 @@
         <v>13951133</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -969,7 +975,7 @@
         <v>1747619</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -980,7 +986,7 @@
         <v>51010813</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -991,7 +997,7 @@
         <v>44810918</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1002,7 +1008,7 @@
         <v>20340994</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1013,7 +1019,7 @@
         <v>4911779</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1024,7 +1030,7 @@
         <v>19033717</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1035,7 +1041,7 @@
         <v>25401606</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1046,7 +1052,7 @@
         <v>30267301</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1057,7 +1063,7 @@
         <v>14124559</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1068,7 +1074,7 @@
         <v>48498051</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1079,7 +1085,7 @@
         <v>25313333</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1090,7 +1096,7 @@
         <v>9823692</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1101,7 +1107,7 @@
         <v>3447341</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1112,7 +1118,7 @@
         <v>18223508</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1123,7 +1129,7 @@
         <v>896842</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1134,7 +1140,7 @@
         <v>5823700</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1145,7 +1151,7 @@
         <v>29228373</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1156,7 +1162,7 @@
         <v>25811332</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1167,7 +1173,7 @@
         <v>1148959</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1178,7 +1184,7 @@
         <v>13707047</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1189,7 +1195,7 @@
         <v>4229593</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1200,7 +1206,7 @@
         <v>28741323</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1211,7 +1217,7 @@
         <v>49180400</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1222,7 +1228,7 @@
         <v>212042</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1233,7 +1239,7 @@
         <v>479510</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1244,7 +1250,7 @@
         <v>335716</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1255,7 +1261,7 @@
         <v>1273719</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1266,7 +1272,7 @@
         <v>3424598</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1277,7 +1283,7 @@
         <v>2981301</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1285,10 +1291,21 @@
         <v>54</v>
       </c>
       <c r="B53">
+        <v>3708025</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54">
         <v>14696986</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>106</v>
+      <c r="C54" s="2" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1306,14 +1323,14 @@
     <hyperlink ref="C12" r:id="rId11" location="!/time/20696550"/>
     <hyperlink ref="C13" r:id="rId12" location="!/time/186283"/>
     <hyperlink ref="C14" r:id="rId13" location="!/time/1863710"/>
-    <hyperlink ref="C15" r:id="rId14" location="!/time/48279389"/>
-    <hyperlink ref="C16" r:id="rId15" location="!/time/25311459"/>
-    <hyperlink ref="C17" r:id="rId16" location="!/time/18642587"/>
-    <hyperlink ref="C18" r:id="rId17" location="!/time/25565675"/>
-    <hyperlink ref="C19" r:id="rId18" location="!/time/18344271"/>
-    <hyperlink ref="C20" r:id="rId19" location="!/time/18421230"/>
-    <hyperlink ref="C21" r:id="rId20" location="!/time/528730"/>
-    <hyperlink ref="C22" r:id="rId21" location="!/time/24468241"/>
+    <hyperlink ref="C15" r:id="rId14" location="!/time/25311459"/>
+    <hyperlink ref="C16" r:id="rId15" location="!/time/18642587"/>
+    <hyperlink ref="C17" r:id="rId16" location="!/time/25565675"/>
+    <hyperlink ref="C18" r:id="rId17" location="!/time/18344271"/>
+    <hyperlink ref="C19" r:id="rId18" location="!/time/18421230"/>
+    <hyperlink ref="C20" r:id="rId19" location="!/time/528730"/>
+    <hyperlink ref="C21" r:id="rId20" location="!/time/24468241"/>
+    <hyperlink ref="C22" r:id="rId21" location="!/time/26243123"/>
     <hyperlink ref="C23" r:id="rId22" location="!/time/13951133"/>
     <hyperlink ref="C24" r:id="rId23" location="!/time/1747619"/>
     <hyperlink ref="C25" r:id="rId24" location="!/time/51010813"/>
@@ -1344,7 +1361,8 @@
     <hyperlink ref="C50" r:id="rId49" location="!/time/1273719"/>
     <hyperlink ref="C51" r:id="rId50" location="!/time/3424598"/>
     <hyperlink ref="C52" r:id="rId51" location="!/time/2981301"/>
-    <hyperlink ref="C53" r:id="rId52" location="!/time/14696986"/>
+    <hyperlink ref="C53" r:id="rId52" location="!/time/3708025"/>
+    <hyperlink ref="C54" r:id="rId53" location="!/time/14696986"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
